--- a/Docs/QA-Testing/Test_Case_WhiteBox.xlsx
+++ b/Docs/QA-Testing/Test_Case_WhiteBox.xlsx
@@ -1,40 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20398"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\MouseWithoutBorders\sp3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97837850-651A-48AF-BBA2-511C1F658DA4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960D02AF-B338-44D6-93F4-710613FAA9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11505" xr2:uid="{9B43A760-E7C9-4B1A-A514-38BB5ECB6014}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9B43A760-E7C9-4B1A-A514-38BB5ECB6014}"/>
   </bookViews>
   <sheets>
     <sheet name="UNIT-TEST-BVA" sheetId="6" r:id="rId1"/>
+    <sheet name="Path_CFG_Mapping" sheetId="7" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="127">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -149,9 +141,6 @@
     <t>100% / 100%</t>
   </si>
   <si>
-    <t>93% / 100%</t>
-  </si>
-  <si>
     <t>Unit Test / Test Method</t>
   </si>
   <si>
@@ -228,32 +217,6 @@
     <t>Password = 3 được chấp nhận</t>
   </si>
   <si>
-    <t>Service vẫn save password = 2</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Service vẫn gọi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>save()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, không exception</t>
-    </r>
-  </si>
-  <si>
     <r>
       <t>ProductInfo.productStock</t>
     </r>
@@ -280,17 +243,250 @@
     <t>ProductInfo.productPrice</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Service vẫn gọi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>repository.save()</t>
-    </r>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Aligned with BvaBoundaryTest + mvn test 181.</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Password = 2 bị từ chối (ConstraintViolation / không save)</t>
+  </si>
+  <si>
+    <t>Quantity = 0 bị từ chối</t>
+  </si>
+  <si>
+    <t>Price = -1 có ConstraintViolation (@Positive / @DecimalMin)</t>
+  </si>
+  <si>
+    <t>Không save; reject validation</t>
+  </si>
+  <si>
+    <t>BVA validation: sheet WB-BVA-*.</t>
+  </si>
+  <si>
+    <t>Path/CFG/Condition: sheet này — map 1-1 Coverage_Report.md mục 5–14.</t>
+  </si>
+  <si>
+    <t>Tổng Unit: 181 tests; Service Layer 100%/100% (mvn test + jacoco).</t>
+  </si>
+  <si>
+    <t>Unit Test / Method</t>
+  </si>
+  <si>
+    <t>Path / Branch</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>WB-PATH-F1</t>
+  </si>
+  <si>
+    <t>finishStatusCanceledTest, finishStatusFinishedTest</t>
+  </si>
+  <si>
+    <t>OrderServiceImpl.finish</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>F-P1 status ≠ NEW</t>
+  </si>
+  <si>
+    <t>throw ORDER_STATUS_ERROR</t>
+  </si>
+  <si>
+    <t>throw</t>
+  </si>
+  <si>
+    <t>WB-PATH-F2</t>
+  </si>
+  <si>
+    <t>finishSuccessTest</t>
+  </si>
+  <si>
+    <t>finish</t>
+  </si>
+  <si>
+    <t>F-P2 status = NEW</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>WB-PATH-C1</t>
+  </si>
+  <si>
+    <t>cancelStatusCanceledTest, cancelStatusFinishTest</t>
+  </si>
+  <si>
+    <t>cancel</t>
+  </si>
+  <si>
+    <t>C-P1 status ≠ NEW</t>
+  </si>
+  <si>
+    <t>exception</t>
+  </si>
+  <si>
+    <t>WB-PATH-C2</t>
+  </si>
+  <si>
+    <t>cancelNoProduct</t>
+  </si>
+  <si>
+    <t>C-P2 products rỗng</t>
+  </si>
+  <si>
+    <t>cancel OK</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>WB-PATH-C3</t>
+  </si>
+  <si>
+    <t>cancelSuccessTest</t>
+  </si>
+  <si>
+    <t>C-P3 productInfo ≠ null</t>
+  </si>
+  <si>
+    <t>increaseStock</t>
+  </si>
+  <si>
+    <t>verify</t>
+  </si>
+  <si>
+    <t>WB-PATH-C4</t>
+  </si>
+  <si>
+    <t>cancelProductInfoNotFoundTest</t>
+  </si>
+  <si>
+    <t>C-P4 productInfo == null</t>
+  </si>
+  <si>
+    <t>không increaseStock</t>
+  </si>
+  <si>
+    <t>never()</t>
+  </si>
+  <si>
+    <t>WB-PATH-M1</t>
+  </si>
+  <si>
+    <t>mergeLocalCartEmptyCollectionTest</t>
+  </si>
+  <si>
+    <t>mergeLocalCart</t>
+  </si>
+  <si>
+    <t>M-P1 collection rỗng</t>
+  </si>
+  <si>
+    <t>empty path, no NPE</t>
+  </si>
+  <si>
+    <t>WB-PATH-M2</t>
+  </si>
+  <si>
+    <t>mergeLocalCartTest, mergeLocalCartTwoProductTest</t>
+  </si>
+  <si>
+    <t>M-P2 đã có SP</t>
+  </si>
+  <si>
+    <t>merge qty</t>
+  </si>
+  <si>
+    <t>WB-PATH-M3</t>
+  </si>
+  <si>
+    <t>mergeLocalCartNoProductTest</t>
+  </si>
+  <si>
+    <t>M-P3 chưa có</t>
+  </si>
+  <si>
+    <t>add mới</t>
+  </si>
+  <si>
+    <t>WB-PATH-D1</t>
+  </si>
+  <si>
+    <t>deleteNoProductTest</t>
+  </si>
+  <si>
+    <t>delete</t>
+  </si>
+  <si>
+    <t>Condition A||B</t>
+  </si>
+  <si>
+    <t>A = T</t>
+  </si>
+  <si>
+    <t>MyException</t>
+  </si>
+  <si>
+    <t>WB-PATH-D2</t>
+  </si>
+  <si>
+    <t>deleteNoUserTest</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
+    <t>A=F, B=T</t>
+  </si>
+  <si>
+    <t>WB-PATH-D3</t>
+  </si>
+  <si>
+    <t>deleteTest</t>
+  </si>
+  <si>
+    <t>A=F, B=F</t>
+  </si>
+  <si>
+    <t>deleteById</t>
+  </si>
+  <si>
+    <t>WB-PROD-01</t>
+  </si>
+  <si>
+    <t>findUpAllTest</t>
+  </si>
+  <si>
+    <t>ProductServiceImpl.findUpAll</t>
+  </si>
+  <si>
+    <t>method từng 0%</t>
+  </si>
+  <si>
+    <t>page data</t>
+  </si>
+  <si>
+    <t>WB-PROD-02</t>
+  </si>
+  <si>
+    <t>findAllInCategoryTest / EmptyPage</t>
+  </si>
+  <si>
+    <t>findAllInCategory</t>
   </si>
 </sst>
 </file>
@@ -360,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -376,6 +572,15 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -691,25 +896,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE6C22E-B1A6-4B4D-867C-4780A0308723}">
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="49.9" customHeight="1"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="49.95" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="49.9" customHeight="1">
+    <row r="1" spans="1:9" ht="49.95" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>12</v>
@@ -726,8 +931,14 @@
       <c r="G1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="49.9" customHeight="1">
+      <c r="H1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="49.95" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -735,7 +946,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>16</v>
@@ -744,13 +955,19 @@
         <v>17</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="49.9" customHeight="1">
+        <v>32</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="49.95" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -758,7 +975,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>16</v>
@@ -767,13 +984,19 @@
         <v>17</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="49.9" customHeight="1">
+        <v>33</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="49.95" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -790,13 +1013,19 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="49.9" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="49.95" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -813,13 +1042,19 @@
         <v>30</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="49.9" customHeight="1">
+        <v>50</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="49.95" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -836,13 +1071,19 @@
         <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="49.9" customHeight="1">
+        <v>38</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="49.95" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -850,7 +1091,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>16</v>
@@ -859,13 +1100,19 @@
         <v>17</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="49.9" customHeight="1">
+        <v>32</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="49.95" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -873,7 +1120,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>16</v>
@@ -882,13 +1129,19 @@
         <v>17</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="49.9" customHeight="1">
+        <v>33</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="49.95" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
@@ -896,7 +1149,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>16</v>
@@ -905,13 +1158,19 @@
         <v>17</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="49.9" customHeight="1">
+        <v>51</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="49.95" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -925,12 +1184,443 @@
         <v>23</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22995342-C17B-4738-BAC5-664B87371A10}">
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" customWidth="1"/>
+    <col min="6" max="6" width="23.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="43.2">
+      <c r="A4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="86.4">
+      <c r="A5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="43.2">
+      <c r="A6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="86.4">
+      <c r="A7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="43.2">
+      <c r="A8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="43.2">
+      <c r="A9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="57.6">
+      <c r="A10" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="72">
+      <c r="A11" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="100.8">
+      <c r="A12" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="57.6">
+      <c r="A13" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="43.2">
+      <c r="A14" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="28.8">
+      <c r="A15" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="28.8">
+      <c r="A16" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="57.6">
+      <c r="A17" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="72">
+      <c r="A18" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>48</v>
       </c>
     </row>

--- a/Docs/QA-Testing/Test_Case_WhiteBox.xlsx
+++ b/Docs/QA-Testing/Test_Case_WhiteBox.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960D02AF-B338-44D6-93F4-710613FAA9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C71789-8E4A-4514-91E4-FE642DFEB373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9B43A760-E7C9-4B1A-A514-38BB5ECB6014}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9B43A760-E7C9-4B1A-A514-38BB5ECB6014}"/>
   </bookViews>
   <sheets>
     <sheet name="UNIT-TEST-BVA" sheetId="6" r:id="rId1"/>
     <sheet name="Path_CFG_Mapping" sheetId="7" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -115,61 +115,12 @@
     <t>testSaveProductNegativePrice()</t>
   </si>
   <si>
-    <r>
-      <t>ProductServiceImpl.save()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>update()</t>
-    </r>
-  </si>
-  <si>
     <t>100% / 100%</t>
   </si>
   <si>
     <t>Unit Test / Test Method</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Validator trả về </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>ConstraintViolation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Không có </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>ConstraintViolation</t>
-    </r>
-  </si>
-  <si>
     <t>Quantity = 0 phải bị từ chối</t>
   </si>
   <si>
@@ -182,29 +133,6 @@
     <t>@Size(min=3)</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Service gọi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>save()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> thành công</t>
-    </r>
-  </si>
-  <si>
     <t>Stock = -1 phải bị từ chối</t>
   </si>
   <si>
@@ -217,29 +145,6 @@
     <t>Password = 3 được chấp nhận</t>
   </si>
   <si>
-    <r>
-      <t>ProductInfo.productStock</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>@Min(0)</t>
-    </r>
-  </si>
-  <si>
     <t>ProductInfo.productPrice</t>
   </si>
   <si>
@@ -487,13 +392,28 @@
   </si>
   <si>
     <t>findAllInCategory</t>
+  </si>
+  <si>
+    <t>Validator trả về ConstraintViolation</t>
+  </si>
+  <si>
+    <t>Không có ConstraintViolation</t>
+  </si>
+  <si>
+    <t>Service gọi save() thành công</t>
+  </si>
+  <si>
+    <t>ProductInfo.productStock – @Min(0)</t>
+  </si>
+  <si>
+    <t>ProductServiceImpl.save() → update()</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,19 +423,19 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial Unicode MS"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -525,6 +445,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -561,26 +493,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -897,306 +829,308 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE6C22E-B1A6-4B4D-867C-4780A0308723}">
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="49.95" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="11.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="49.95" customHeight="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="G5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="H5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="49.95" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="H9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="49.95" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="H10" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="49.95" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="5">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="49.95" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="49.95" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="49.95" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="49.95" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="49.95" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="49.95" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1208,420 +1142,421 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22995342-C17B-4738-BAC5-664B87371A10}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.21875" customWidth="1"/>
-    <col min="6" max="6" width="23.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="G4" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="43.2">
-      <c r="A4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="B5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="C5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="D5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="E5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="86.4">
-      <c r="A5" s="8" t="s">
+      <c r="F5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="G5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="H5" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="B6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="C6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="D6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="F6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="43.2">
-      <c r="A6" s="8" t="s">
+      <c r="G6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="86.4">
-      <c r="A7" s="8" t="s">
+      <c r="H7" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="8" t="s">
+      <c r="F8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G8" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="43.2">
-      <c r="A8" s="8" t="s">
+      <c r="H8" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="8" t="s">
+      <c r="C9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F9" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="43.2">
-      <c r="A9" s="8" t="s">
+      <c r="H9" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B10" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="C10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="57.6">
-      <c r="A10" s="8" t="s">
+      <c r="H10" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B11" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="8" t="s">
+      <c r="C11" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="D11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="F11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="72">
-      <c r="A11" s="8" t="s">
+      <c r="G11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B12" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="F12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="G12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="100.8">
-      <c r="A12" s="8" t="s">
+      <c r="B13" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="8" t="s">
+      <c r="F13" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="G13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="57.6">
-      <c r="A13" s="8" t="s">
+      <c r="B14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="C14" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="8" t="s">
+      <c r="D14" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="E14" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="43.2">
-      <c r="A14" s="8" t="s">
+      <c r="F14" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="G14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="B15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="C15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E15" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="28.8">
-      <c r="A15" s="8" t="s">
+      <c r="B16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="F16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="G16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="28.8">
-      <c r="A16" s="8" t="s">
+      <c r="B17" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C17" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="D17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F17" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="57.6">
-      <c r="A17" s="8" t="s">
+      <c r="G17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B18" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C18" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="72">
-      <c r="A18" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>48</v>
+      <c r="E18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
